--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-process-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-process-medium.xlsx
@@ -460,19 +460,19 @@
         <v>V-Model ánh xạ trực tiếp các mức test với các giai đoạn thiết kế: Unit Test đối chiếu với Detailed Design; Integration Test đối chiếu với High-level Design; System Test đối chiếu với SRS; Acceptance Test đối chiếu với Business Needs.</v>
       </c>
       <c r="F2" t="str">
+        <v>User Business Needs — Nhu cầu nghiệp vụ thực tế của người dùng cuối — nhu cầu nghiệp vụ</v>
+      </c>
+      <c r="G2" t="str">
         <v>Component Design / Detailed Design — Thiết kế chi tiết thành phần/mã nguồn — thiết kế chi tiết</v>
-      </c>
-      <c r="G2" t="str">
-        <v>System Architecture / High-Level Design — Thiết kế kiến trúc hệ thống cấp cao — thiết kế hệ thống</v>
       </c>
       <c r="H2" t="str">
         <v>Requirements Specification (SRS) — Tài liệu đặc tả yêu cầu phần mềm cấp cao — tài liệu yêu cầu</v>
       </c>
       <c r="I2" t="str">
-        <v>User Business Needs — Nhu cầu nghiệp vụ thực tế của người dùng cuối — nhu cầu nghiệp vụ</v>
+        <v>System Architecture / High-Level Design — Thiết kế kiến trúc hệ thống cấp cao — thiết kế hệ thống</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Bug Density (ví dụ: 2 bugs/1000 lines of code) giúp đánh giá chất lượng mã nguồn. Defect Leakage (ví dụ: 10% bugs bị khách hàng tìm thấy ở UAT) phản ánh trực tiếp hiệu quả và chất lượng của quy trình test của team QA.</v>
       </c>
       <c r="F3" t="str">
+        <v>Bug Density đo lường tốc độ phản hồi của trang web; Defect Leakage đo lường tốc độ rò rỉ bộ nhớ RAM — chỉ số hiệu năng phần cứng</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Bug Density do PM tính toán; Defect Leakage do QA Leader bắt buộc phải chịu trách nhiệm bồi thường tiền — trách nhiệm nhân sự</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Bug Density chỉ dùng cho kiểm thử tự động; Defect Leakage chỉ dùng cho kiểm thử thủ công — phân loại phương pháp test</v>
+      </c>
+      <c r="I3" t="str">
         <v>Bug Density tính bằng số lỗi chia cho kích thước phần mềm (ví dụ: KLOC); Defect Leakage tính bằng tỷ lệ lỗi bị bỏ sót trôi lên môi trường UAT/Production chia cho tổng số lỗi — lỗi trên kích thước vs lỗi bỏ sót lên môi trường sau</v>
       </c>
-      <c r="G3" t="str">
-        <v>Bug Density chỉ dùng cho kiểm thử tự động; Defect Leakage chỉ dùng cho kiểm thử thủ công — phân loại phương pháp test</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Bug Density do PM tính toán; Defect Leakage do QA Leader bắt buộc phải chịu trách nhiệm bồi thường tiền — trách nhiệm nhân sự</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Bug Density đo lường tốc độ phản hồi của trang web; Defect Leakage đo lường tốc độ rò rỉ bộ nhớ RAM — chỉ số hiệu năng phần cứng</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Một Bug Report tốt phải giúp dev tái hiện lại được lỗi (Reproducible). Các bước thực hiện rõ ràng, dữ liệu test cụ thể và bằng chứng (screenshot, video, console logs) là chìa khóa để dev định vị vùng code lỗi.</v>
       </c>
       <c r="F4" t="str">
-        <v>Steps to Reproduce (Các bước tái hiện), Expected Result (Kết quả mong đợi) và Actual Result (Kết quả thực tế xảy ra) kèm theo log/ảnh chụp màn hình — thông tin kỹ thuật tái hiện lỗi</v>
+        <v>Đoạn mã code sửa lỗi gợi ý viết bằng ngôn ngữ lập trình Java của QA — code sửa lỗi gợi ý</v>
       </c>
       <c r="G4" t="str">
         <v>Tên và mức lương hiện tại của kiểm thử viên đã tìm ra lỗi đó — thông tin nhân sự tìm lỗi</v>
       </c>
       <c r="H4" t="str">
-        <v>Đoạn mã code sửa lỗi gợi ý viết bằng ngôn ngữ lập trình Java của QA — code sửa lỗi gợi ý</v>
+        <v>Steps to Reproduce (Các bước tái hiện), Expected Result (Kết quả mong đợi) và Actual Result (Kết quả thực tế xảy ra) kèm theo log/ảnh chụp màn hình — thông tin kỹ thuật tái hiện lỗi</v>
       </c>
       <c r="I4" t="str">
         <v>Số lượng khách hàng tối đa sẽ bị ảnh hưởng bởi lỗi này trong tương lai — ước lượng tác động khách hàng</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -562,10 +562,10 @@
         <v>Xác định xem lập trình viên nào được phép vào và ra khỏi phòng máy chủ của dự án — kiểm soát ra vào vật lý</v>
       </c>
       <c r="H5" t="str">
+        <v>Định nghĩa mức chi phí tối thiểu và tối đa được phép chi tiêu cho công cụ kiểm thử tự động — kiểm soát chi phí công cụ</v>
+      </c>
+      <c r="I5" t="str">
         <v>Xác định số lượng test case tối đa được phép viết và xóa bỏ trong một ngày — giới hạn số lượng test case</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Định nghĩa mức chi phí tối thiểu và tối đa được phép chi tiêu cho công cụ kiểm thử tự động — kiểm soát chi phí công cụ</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -588,19 +588,19 @@
         <v>Đây là trường hợp kinh điển: Lỗi không phá hủy tính năng (Severity Low) nhưng ảnh hưởng nặng đến thương hiệu/người dùng lớn (Priority High). Điều này chứng minh Severity và Priority không phải lúc nào cũng đi đôi với nhau.</v>
       </c>
       <c r="F6" t="str">
+        <v>Severity: Critical; Priority: High — lỗi làm hỏng toàn bộ tính năng thanh toán của ứng dụng di động — lỗi nghiêm trọng</v>
+      </c>
+      <c r="G6" t="str">
         <v>Severity: Low (Lỗi giao diện nhẹ không hỏng chức năng); Priority: High (Cần sửa gấp vì ảnh hưởng nghiêm trọng đến hình ảnh thương hiệu và trải nghiệm khách hàng VIP) — Severity thấp - Priority cao</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Severity: High (Sập hệ thống); Priority: Low (Không cần sửa trong vòng một năm tới) — Severity cao - Priority thấp</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Severity: Critical; Priority: High — lỗi làm hỏng toàn bộ tính năng thanh toán của ứng dụng di động — lỗi nghiêm trọng</v>
       </c>
       <c r="I6" t="str">
         <v>Severity: Low; Priority: Low — lỗi giao diện nhỏ ở màn hình ẩn sâu bên trong tài liệu hướng dẫn — lỗi nhỏ ít tương tác</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Trong Scrum, QA là một phần của Development Team. QA thực hiện phân tích yêu cầu ở buổi planning, viết test case ở các ngày đầu sprint, test liên tục (in-sprint testing) để đảm bảo User Story đạt DoD vào cuối sprint.</v>
       </c>
       <c r="F7" t="str">
+        <v>QA ngồi chơi trong 2 tuần đầu và chỉ bắt đầu làm việc khi Sprint đã kết thúc hoàn toàn — kiểm thử cuối kỳ</v>
+      </c>
+      <c r="G7" t="str">
+        <v>QA bắt buộc phải ngồi chung phòng và dùng chung máy tính với Product Owner khi chạy test — ngồi chung máy tính</v>
+      </c>
+      <c r="H7" t="str">
         <v>QA tham gia ngay từ đầu Sprint, viết test case dựa trên User Story/AC và thực hiện test liên tục ngay khi dev bàn giao từng phần tính năng — kiểm thử liên tục trong Sprint</v>
       </c>
-      <c r="G7" t="str">
-        <v>QA ngồi chơi trong 2 tuần đầu và chỉ bắt đầu làm việc khi Sprint đã kết thúc hoàn toàn — kiểm thử cuối kỳ</v>
-      </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>QA chỉ làm nhiệm vụ viết báo cáo lỗi, toàn bộ việc chạy test do lập trình viên tự thực hiện — lập trình viên tự test</v>
       </c>
-      <c r="I7" t="str">
-        <v>QA bắt buộc phải ngồi chung phòng và dùng chung máy tính với Product Owner khi chạy test — ngồi chung máy tính</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>RTM (Ma trận truy vết yêu cầu) liên kết: Yêu cầu nghiệp vụ -&gt; Test Case -&gt; Bug ID. RTM giúp QA kiểm soát xem có yêu cầu nào bị bỏ sót không có test case (thiếu coverage) hoặc có test case nào chạy fail mà chưa được log bug không.</v>
       </c>
       <c r="F8" t="str">
+        <v>Tính toán tổng số lỗi tối đa mà hệ thống có thể gặp phải trước khi sập máy chủ — dự báo lỗi hệ thống</v>
+      </c>
+      <c r="G8" t="str">
         <v>Ánh xạ các yêu cầu nghiệp vụ với các test case tương ứng để đảm bảo 100% yêu cầu đều được thiết kế kịch bản kiểm thử — bảo đảm độ bao phủ yêu cầu (Test Coverage)</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Theo dõi thời gian đi làm và ra về hàng ngày của các lập trình viên trong công ty — chấm công nhân sự</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>Tự động chạy các kịch bản kiểm thử tự động trên môi trường Jenkins CI/CD — chạy test tự động</v>
       </c>
-      <c r="I8" t="str">
-        <v>Tính toán tổng số lỗi tối đa mà hệ thống có thể gặp phải trước khi sập máy chủ — dự báo lỗi hệ thống</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Trạng thái Deferred nghĩa là lỗi được ghi nhận nhưng bị hoãn sửa (thường do độ ưu tiên thấp, sắp đến ngày release, hoặc sửa lỗi này có nguy cơ phá vỡ các tính năng khác lớn hơn).</v>
       </c>
       <c r="F9" t="str">
-        <v>Khi PO hoặc PM xác nhận lỗi có tồn tại nhưng quyết định hoãn sửa sang các bản release tiếp theo do không kịp tiến độ hoặc lỗi quá nhẹ — hoãn sửa lỗi có chủ đích</v>
+        <v>Khi hệ thống tự động sửa lỗi thành công mà không cần lập trình viên can thiệp — tự động sửa lỗi</v>
       </c>
       <c r="G9" t="str">
         <v>Khi Developer đã sửa xong lỗi và đang đợi QA chạy kiểm thử để đóng bug — chờ kiểm thử lại</v>
       </c>
       <c r="H9" t="str">
+        <v>Khi PO hoặc PM xác nhận lỗi có tồn tại nhưng quyết định hoãn sửa sang các bản release tiếp theo do không kịp tiến độ hoặc lỗi quá nhẹ — hoãn sửa lỗi có chủ đích</v>
+      </c>
+      <c r="I9" t="str">
         <v>Khi QA phát hiện ra lỗi nhưng tự ý xóa bỏ bản ghi lỗi đó ra khỏi hệ thống Jira — tự ý xóa lỗi</v>
       </c>
-      <c r="I9" t="str">
-        <v>Khi hệ thống tự động sửa lỗi thành công mà không cần lập trình viên can thiệp — tự động sửa lỗi</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Báo cáo tiến độ chạy test hàng ngày giúp PM và khách hàng biết được team test đã đi được bao xa (ví dụ: đã chạy 80% test cases, tỷ lệ pass đạt 90%, bị blocked 5% do môi trường lỗi).</v>
       </c>
       <c r="F10" t="str">
+        <v>Tổng chi phí bản quyền phần mềm đã mua cho công cụ Jira và Confluence — chi phí phần mềm</v>
+      </c>
+      <c r="G10" t="str">
         <v>Tỷ lệ phần trăm các test case ở trạng thái: Passed, Failed, Blocked, và Untested (Chưa chạy) — phân bổ trạng thái thực thi</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Số lượng dòng code Java đã viết thành công so với kế hoạch ban đầu — tiến độ viết code</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Tổng chi phí bản quyền phần mềm đã mua cho công cụ Jira và Confluence — chi phí phần mềm</v>
       </c>
       <c r="I10" t="str">
         <v>Số lượng nhân viên QA đã xin nghỉ phép trong quá trình dự án đang chạy test — nhân sự nghỉ phép</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>DoR là bộ tiêu chí kiểm tra xem một User Story đã đủ điều kiện để đưa vào phát triển chưa. Story chưa đạt DoR (mơ hồ, thiếu AC) sẽ khiến dev code sai và QA không thể thiết kế test case vì không biết thế nào là kết quả mong đợi đúng.</v>
       </c>
       <c r="F11" t="str">
+        <v>DoR yêu cầu khách hàng phải ký cam kết không được thay đổi ý kiến trong suốt một năm — khóa yêu cầu tuyệt đối</v>
+      </c>
+      <c r="G11" t="str">
+        <v>DoR tự động tạo ra các kịch bản kiểm thử tự động trên công cụ Postman cho QA — tự động sinh test</v>
+      </c>
+      <c r="H11" t="str">
         <v>DoR đảm bảo User Story đã đầy đủ thông tin mô tả và tiêu chí nghiệm thu rõ ràng, giúp QA có đủ căn cứ logic để thiết kế test case chuẩn xác — đảm bảo chất lượng đầu vào của yêu cầu</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>DoR bắt buộc lập trình viên phải viết xong code trước khi QA bắt đầu viết kịch bản test — đảo lộn thứ tự quy trình</v>
       </c>
-      <c r="H11" t="str">
-        <v>DoR tự động tạo ra các kịch bản kiểm thử tự động trên công cụ Postman cho QA — tự động sinh test</v>
-      </c>
-      <c r="I11" t="str">
-        <v>DoR yêu cầu khách hàng phải ký cam kết không được thay đổi ý kiến trong suốt một năm — khóa yêu cầu tuyệt đối</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
